--- a/Documents/เฉพาะคราว/SA_Spec_Narcotic4_Temporary_IMP_rev.1.5.xlsx
+++ b/Documents/เฉพาะคราว/SA_Spec_Narcotic4_Temporary_IMP_rev.1.5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\NCSystem\brain_NCSYSTEM\Documents\เฉพาะคราว\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964B337E-F254-4592-B963-91B25ACC112D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42128AB4-27E2-4173-BC0C-BBD33A7968A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="524">
   <si>
     <t>Step 3: ยาเสพติดให้โทษที่ขอนำเข้า (ส่วนที่ ๒.๖) ⭐ — Dynamic Table, 2-Tier Content Model</t>
   </si>
@@ -908,12 +908,6 @@
     <t>1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">ใช้ pattern เดียวกับ Z4_NarcoticCancellation/Edit/Renewal/Replacement
-แสดงข้อมูลใบอนุญาตเฉพาะกรณี
-1. 
-2. </t>
-  </si>
-  <si>
     <t>เลขประจำตัวประชาชน / นิติบุคคล</t>
   </si>
   <si>
@@ -962,13 +956,6 @@
     <t>readonly (auto-fill); max 255</t>
   </si>
   <si>
-    <t xml:space="preserve">เอาข้อมูลเลขนิติบุคคล ไปค้นหาที่ API DOPA แล้วเอาข้อมูลชื่อบุคคล หรือ นิติบุคคล มาใช้
-บันทึก
-- RequisitionParticipant.IdentityType = 3
-- RequisitionParticipant.ParticipantTypeId = 1
-- </t>
-  </si>
-  <si>
     <t>1.2 เหตุผลในการขออนุญาตครั้งนี้</t>
   </si>
   <si>
@@ -1020,9 +1007,6 @@
     <t>ForeignEntityName (where Type='I')</t>
   </si>
   <si>
-    <t>max 500; English only</t>
-  </si>
-  <si>
     <t>2.1</t>
   </si>
   <si>
@@ -1044,9 +1028,6 @@
     <t>nvarchar(1000)</t>
   </si>
   <si>
-    <t>max 1000; English only</t>
-  </si>
-  <si>
     <t>ประเทศผู้นำเข้า</t>
   </si>
   <si>
@@ -1086,9 +1067,6 @@
     <t>ForeignEntityName (where Type='E')</t>
   </si>
   <si>
-    <t>max 500</t>
-  </si>
-  <si>
     <t>2.2</t>
   </si>
   <si>
@@ -1102,9 +1080,6 @@
   </si>
   <si>
     <t>FullAddress (where Type='E')</t>
-  </si>
-  <si>
-    <t>max 1000</t>
   </si>
   <si>
     <t>ประเทศผู้ส่งออก</t>
@@ -1712,6 +1687,45 @@
   <si>
     <t>License (filter: SELECT * FROM NCDB.dbo.License
 WHERE LicenseTypeId IN (47), holder=session user)</t>
+  </si>
+  <si>
+    <t>Input Seq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ใช้ pattern เดียวกับ Z4NarcoticCancellationRequest/NarcoticCancellationDocument
+class="d-flex flex-row align-items-center gap-2 gap-md-4"
+</t>
+  </si>
+  <si>
+    <t>LicenseParticipant.TaxNumber (filter: 
+SELECT Id, LicenseNo FROM dbo.License
+WHERE Id = 192 
+SELECT LicenseId, JuristicName, TaxNumber
+FROM dbo.LicenseParticipant p
+INNER JOIN dbo.License l
+ON p.LicenseId = l.Id 
+WHERE l.Id = 192
+AND p.ParticipantTypeId = 1), holder=session user)</t>
+  </si>
+  <si>
+    <t>LicenseParticipant.JuristicName (filter: 
+SELECT Id, LicenseNo FROM dbo.License
+WHERE Id = 192 
+SELECT LicenseId, JuristicName, TaxNumber
+FROM dbo.LicenseParticipant p
+INNER JOIN dbo.License l
+ON p.LicenseId = l.Id 
+WHERE l.Id = 192
+AND p.ParticipantTypeId = 1), holder=session user)</t>
+  </si>
+  <si>
+    <t>CountryName (filter: SELECT NameEnglish FROM dbo.MasterCountry)</t>
+  </si>
+  <si>
+    <t>FullAddress (filter: SELECT FullAddress FROM dbo.MasterForeignEntity)</t>
+  </si>
+  <si>
+    <t>ForeignEntityName (filter: SELECT ForeignEntityName FROM dbo.MasterForeignEntity)</t>
   </si>
 </sst>
 </file>
@@ -1941,7 +1955,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2013,15 +2027,21 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2036,17 +2056,17 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2538,7 +2558,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="51" t="s">
+      <c r="A28" s="43" t="s">
         <v>195</v>
       </c>
       <c r="B28" s="40"/>
@@ -2549,43 +2569,43 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="42" t="s">
         <v>197</v>
       </c>
       <c r="B31" s="40"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="50" t="s">
+      <c r="A32" s="42" t="s">
         <v>198</v>
       </c>
       <c r="B32" s="40"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="50" t="s">
+      <c r="A33" s="42" t="s">
         <v>199</v>
       </c>
       <c r="B33" s="40"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="50" t="s">
+      <c r="A34" s="42" t="s">
         <v>200</v>
       </c>
       <c r="B34" s="40"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="50" t="s">
+      <c r="A35" s="42" t="s">
         <v>201</v>
       </c>
       <c r="B35" s="40"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="50" t="s">
+      <c r="A36" s="42" t="s">
         <v>202</v>
       </c>
       <c r="B36" s="40"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="50" t="s">
+      <c r="A37" s="42" t="s">
         <v>203</v>
       </c>
       <c r="B37" s="40"/>
@@ -2867,7 +2887,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" ht="110.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="51" t="s">
+      <c r="A28" s="43" t="s">
         <v>249</v>
       </c>
       <c r="B28" s="40"/>
@@ -2882,28 +2902,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="35" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="35" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="15" max="16" width="12" customWidth="1"/>
+    <col min="17" max="17" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="39" t="s">
         <v>250</v>
       </c>
       <c r="B1" s="40"/>
@@ -2921,8 +2942,9 @@
       <c r="N1" s="40"/>
       <c r="O1" s="40"/>
       <c r="P1" s="40"/>
-    </row>
-    <row r="3" spans="1:16" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q1" s="40"/>
+    </row>
+    <row r="3" spans="1:17" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>2</v>
       </c>
@@ -2933,46 +2955,49 @@
         <v>4</v>
       </c>
       <c r="D3" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="F3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="G3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="K3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="L3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="M3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="N3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="O3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="P3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="16" t="s">
+      <c r="Q3" s="16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
         <v>251</v>
       </c>
@@ -2991,8 +3016,9 @@
       <c r="N4" s="40"/>
       <c r="O4" s="40"/>
       <c r="P4" s="40"/>
-    </row>
-    <row r="5" spans="1:16" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q4" s="40"/>
+    </row>
+    <row r="5" spans="1:17" ht="84" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -3002,143 +3028,150 @@
       <c r="C5" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="54">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="F5" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="G5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>521</v>
-      </c>
       <c r="H5" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="I5" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="J5" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="K5" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="K5" s="10" t="s">
-        <v>522</v>
-      </c>
       <c r="L5" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="M5" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="N5" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="N5" s="18" t="s">
+      <c r="O5" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="170.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="54">
+        <v>2.1</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="F6" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="10" t="s">
+      <c r="I6" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="J6" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="K6" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="L6" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="M6" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="K6" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="10" t="s">
+      <c r="N6" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="O6" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="M6" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="N6" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="132" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:17" ht="170.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="D7" s="54">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="F7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="10" t="s">
+      <c r="I7" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="I7" s="10" t="s">
+      <c r="K7" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="L7" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="M7" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="K7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="10" t="s">
+      <c r="N7" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="O7" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+    </row>
+    <row r="9" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="41" t="s">
         <v>276</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="N7" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
-        <v>278</v>
       </c>
       <c r="B9" s="40"/>
       <c r="C9" s="40"/>
@@ -3155,60 +3188,64 @@
       <c r="N9" s="40"/>
       <c r="O9" s="40"/>
       <c r="P9" s="40"/>
-    </row>
-    <row r="10" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q9" s="40"/>
+    </row>
+    <row r="10" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>4</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="D10" s="54">
+        <v>3</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="F10" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="G10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="J10" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="K10" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="10" t="s">
+      <c r="L10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="I10" s="10" t="s">
+      <c r="M10" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="N10" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="K10" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" s="10" t="s">
+      <c r="O10" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10" t="s">
         <v>285</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="N10" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10" t="s">
-        <v>287</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A9:P9"/>
-    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A9:Q9"/>
+    <mergeCell ref="A4:Q4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3216,29 +3253,30 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="35" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="35" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="15" max="16" width="12" customWidth="1"/>
+    <col min="17" max="17" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
-        <v>288</v>
+    <row r="1" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="39" t="s">
+        <v>286</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -3255,8 +3293,9 @@
       <c r="N1" s="40"/>
       <c r="O1" s="40"/>
       <c r="P1" s="40"/>
-    </row>
-    <row r="3" spans="1:16" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q1" s="40"/>
+    </row>
+    <row r="3" spans="1:17" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>2</v>
       </c>
@@ -3267,48 +3306,51 @@
         <v>4</v>
       </c>
       <c r="D3" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="F3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="G3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="H3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="K3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="L3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="M3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="N3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="O3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="P3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="16" t="s">
+      <c r="Q3" s="16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
@@ -3325,152 +3367,158 @@
       <c r="N4" s="40"/>
       <c r="O4" s="40"/>
       <c r="P4" s="40"/>
-    </row>
-    <row r="5" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q4" s="40"/>
+    </row>
+    <row r="5" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" s="54">
+        <v>1.2</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="F5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="J5" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="10" t="s">
+      <c r="K5" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="O5" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="N5" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="D6" s="54">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="K6" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="10" t="s">
+      <c r="L6" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="N6" s="18" t="s">
+      <c r="O6" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="O6" s="10"/>
       <c r="P6" s="10"/>
-    </row>
-    <row r="7" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q6" s="10"/>
+    </row>
+    <row r="7" spans="1:17" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="D7" s="54">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="K7" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="D7" s="10" t="s">
+      <c r="L7" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="M7" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="N7" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="O7" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="J7" s="10" t="s">
+    </row>
+    <row r="9" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="41" t="s">
         <v>308</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="N7" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
-        <v>312</v>
       </c>
       <c r="B9" s="40"/>
       <c r="C9" s="40"/>
@@ -3487,148 +3535,154 @@
       <c r="N9" s="40"/>
       <c r="O9" s="40"/>
       <c r="P9" s="40"/>
-    </row>
-    <row r="10" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q9" s="40"/>
+    </row>
+    <row r="10" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>4</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="D10" s="54">
+        <v>1.2</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="N10" s="18" t="s">
+      <c r="O10" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="10"/>
       <c r="P10" s="10"/>
-    </row>
-    <row r="11" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q10" s="10"/>
+    </row>
+    <row r="11" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>5</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>321</v>
+        <v>315</v>
+      </c>
+      <c r="D11" s="54">
+        <v>2</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="F11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>293</v>
-      </c>
       <c r="I11" s="10" t="s">
-        <v>322</v>
+        <v>291</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>25</v>
+        <v>299</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="N11" s="18" t="s">
+        <v>522</v>
+      </c>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="O11" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="O11" s="10"/>
       <c r="P11" s="10"/>
-    </row>
-    <row r="12" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q11" s="10"/>
+    </row>
+    <row r="12" spans="1:17" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>6</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>326</v>
+        <v>319</v>
+      </c>
+      <c r="D12" s="54">
+        <v>1.1000000000000001</v>
       </c>
       <c r="E12" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="F12" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="G12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="H12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="10" t="s">
-        <v>293</v>
-      </c>
       <c r="I12" s="10" t="s">
-        <v>327</v>
+        <v>291</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>328</v>
+        <v>521</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="N12" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="O12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="O12" s="10"/>
       <c r="P12" s="10"/>
-    </row>
-    <row r="14" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q12" s="10"/>
+    </row>
+    <row r="14" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B14" s="40"/>
       <c r="C14" s="40"/>
@@ -3645,148 +3699,154 @@
       <c r="N14" s="40"/>
       <c r="O14" s="40"/>
       <c r="P14" s="40"/>
-    </row>
-    <row r="15" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q14" s="40"/>
+    </row>
+    <row r="15" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>7</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>332</v>
+        <v>325</v>
+      </c>
+      <c r="D15" s="54">
+        <v>1.2</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>59</v>
+        <v>326</v>
       </c>
       <c r="F15" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="H15" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="10" t="s">
-        <v>293</v>
-      </c>
       <c r="I15" s="10" t="s">
-        <v>333</v>
+        <v>291</v>
       </c>
       <c r="J15" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="K15" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="K15" s="10" t="s">
-        <v>25</v>
-      </c>
       <c r="L15" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="N15" s="18" t="s">
+        <v>523</v>
+      </c>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="O15" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="O15" s="10"/>
       <c r="P15" s="10"/>
-    </row>
-    <row r="16" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q15" s="10"/>
+    </row>
+    <row r="16" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>8</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>337</v>
+        <v>330</v>
+      </c>
+      <c r="D16" s="54">
+        <v>2</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>282</v>
+        <v>331</v>
       </c>
       <c r="F16" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="H16" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="10" t="s">
-        <v>293</v>
-      </c>
       <c r="I16" s="10" t="s">
-        <v>338</v>
+        <v>291</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>25</v>
+        <v>299</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="N16" s="18" t="s">
+        <v>522</v>
+      </c>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="O16" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="O16" s="10"/>
       <c r="P16" s="10"/>
-    </row>
-    <row r="17" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q16" s="10"/>
+    </row>
+    <row r="17" spans="1:17" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>9</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>341</v>
+        <v>334</v>
+      </c>
+      <c r="D17" s="54">
+        <v>1.1000000000000001</v>
       </c>
       <c r="E17" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="G17" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="H17" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="10" t="s">
-        <v>293</v>
-      </c>
       <c r="I17" s="10" t="s">
-        <v>342</v>
+        <v>291</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="L17" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="N17" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="M17" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="N17" s="18" t="s">
+      <c r="O17" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="O17" s="10"/>
       <c r="P17" s="10"/>
-    </row>
-    <row r="19" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q17" s="10"/>
+    </row>
+    <row r="19" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B19" s="40"/>
       <c r="C19" s="40"/>
@@ -3803,152 +3863,162 @@
       <c r="N19" s="40"/>
       <c r="O19" s="40"/>
       <c r="P19" s="40"/>
-    </row>
-    <row r="20" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q19" s="40"/>
+    </row>
+    <row r="20" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>10</v>
       </c>
       <c r="B20" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="D20" s="54">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L20" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="M20" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="N20" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="D20" s="10" t="s">
+      <c r="O20" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="L20" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="M20" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="N20" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>11</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>353</v>
+        <v>346</v>
+      </c>
+      <c r="D21" s="55">
+        <v>1.2</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F21" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="H21" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="I21" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="I21" s="10" t="s">
-        <v>347</v>
-      </c>
       <c r="J21" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="K21" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="K21" s="10" t="s">
-        <v>354</v>
-      </c>
       <c r="L21" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="N21" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="O21" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="O21" s="10"/>
       <c r="P21" s="10"/>
-    </row>
-    <row r="22" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q21" s="10"/>
+    </row>
+    <row r="22" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>12</v>
       </c>
       <c r="B22" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="D22" s="54">
+        <v>1.3</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="J22" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="K22" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="L22" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="M22" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="N22" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="O22" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="F22" s="10" t="s">
+    </row>
+    <row r="24" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="41" t="s">
         <v>359</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="L22" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="N22" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="41" t="s">
-        <v>365</v>
       </c>
       <c r="B24" s="40"/>
       <c r="C24" s="40"/>
@@ -3965,63 +4035,67 @@
       <c r="N24" s="40"/>
       <c r="O24" s="40"/>
       <c r="P24" s="40"/>
-    </row>
-    <row r="25" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q24" s="40"/>
+    </row>
+    <row r="25" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>13</v>
       </c>
       <c r="B25" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="D25" s="54">
+        <v>1</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="O25" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10" t="s">
         <v>366</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="N25" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10" t="s">
-        <v>372</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A14:P14"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A9:P9"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="A24:P24"/>
-    <mergeCell ref="A19:P19"/>
+    <mergeCell ref="A14:Q14"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A9:Q9"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A24:Q24"/>
+    <mergeCell ref="A19:Q19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4050,7 +4124,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="40"/>
@@ -4070,7 +4144,7 @@
       <c r="P1" s="40"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="40"/>
@@ -4762,7 +4836,7 @@
       </c>
     </row>
     <row r="20" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="47" t="s">
+      <c r="A20" s="49" t="s">
         <v>90</v>
       </c>
       <c r="B20" s="40"/>
@@ -4782,7 +4856,7 @@
       <c r="P20" s="40"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="48" t="s">
+      <c r="A21" s="50" t="s">
         <v>91</v>
       </c>
       <c r="B21" s="40"/>
@@ -4802,13 +4876,13 @@
       <c r="P21" s="40"/>
     </row>
     <row r="22" spans="1:16" ht="144" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="46" t="s">
         <v>92</v>
       </c>
       <c r="C22" s="40"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="39" t="s">
+      <c r="A23" s="45" t="s">
         <v>93</v>
       </c>
       <c r="B23" s="40"/>
@@ -4879,7 +4953,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="39" t="s">
+      <c r="A35" s="45" t="s">
         <v>108</v>
       </c>
       <c r="B35" s="40"/>
@@ -4950,7 +5024,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="39" t="s">
+      <c r="A47" s="45" t="s">
         <v>116</v>
       </c>
       <c r="B47" s="40"/>
@@ -5021,7 +5095,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="39" t="s">
+      <c r="A59" s="45" t="s">
         <v>122</v>
       </c>
       <c r="B59" s="40"/>
@@ -5038,7 +5112,7 @@
       <c r="E62" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="F62" s="44" t="s">
+      <c r="F62" s="46" t="s">
         <v>124</v>
       </c>
       <c r="G62" s="40"/>
@@ -5048,7 +5122,7 @@
       <c r="E63" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="F63" s="46" t="s">
+      <c r="F63" s="48" t="s">
         <v>126</v>
       </c>
       <c r="G63" s="40"/>
@@ -5074,7 +5148,7 @@
       <c r="E66" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="F66" s="46" t="s">
+      <c r="F66" s="48" t="s">
         <v>130</v>
       </c>
       <c r="G66" s="40"/>
@@ -5114,7 +5188,7 @@
       </c>
     </row>
     <row r="74" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="45" t="s">
+      <c r="A74" s="47" t="s">
         <v>134</v>
       </c>
       <c r="B74" s="40"/>
@@ -5134,7 +5208,7 @@
       <c r="P74" s="40"/>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A75" s="42" t="s">
+      <c r="A75" s="44" t="s">
         <v>135</v>
       </c>
       <c r="B75" s="40"/>
@@ -5154,7 +5228,7 @@
       <c r="P75" s="40"/>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A76" s="42" t="s">
+      <c r="A76" s="44" t="s">
         <v>136</v>
       </c>
       <c r="B76" s="40"/>
@@ -5174,7 +5248,7 @@
       <c r="P76" s="40"/>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A77" s="42" t="s">
+      <c r="A77" s="44" t="s">
         <v>137</v>
       </c>
       <c r="B77" s="40"/>
@@ -5248,6 +5322,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A77:P77"/>
     <mergeCell ref="A59:D59"/>
@@ -5264,7 +5339,6 @@
     <mergeCell ref="A5:P5"/>
     <mergeCell ref="A75:P75"/>
     <mergeCell ref="A76:P76"/>
-    <mergeCell ref="A35:D35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -5294,8 +5368,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
-        <v>373</v>
+      <c r="A1" s="39" t="s">
+        <v>367</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -5365,7 +5439,7 @@
     </row>
     <row r="4" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="53" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
@@ -5385,7 +5459,7 @@
     </row>
     <row r="5" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B5" s="40"/>
       <c r="C5" s="40"/>
@@ -5408,36 +5482,36 @@
         <v>1</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>372</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M6" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>378</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N6" s="18" t="s">
         <v>28</v>
@@ -5450,38 +5524,38 @@
         <v>2</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="G7" s="27"/>
       <c r="H7" s="10" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="N7" s="18" t="s">
         <v>28</v>
@@ -5494,34 +5568,34 @@
         <v>3</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="G8" s="27"/>
       <c r="H8" s="10" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="N8" s="18" t="s">
         <v>28</v>
@@ -5531,7 +5605,7 @@
     </row>
     <row r="10" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="52" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B10" s="40"/>
       <c r="C10" s="40"/>
@@ -5554,36 +5628,36 @@
         <v>1</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I11" s="27" t="s">
+        <v>374</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M11" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G11" s="27" t="s">
-        <v>391</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I11" s="27" t="s">
-        <v>380</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N11" s="18" t="s">
         <v>28</v>
@@ -5596,40 +5670,40 @@
         <v>2</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G12" s="27" t="s">
         <v>385</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="E12" s="10" t="s">
+      <c r="H12" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I12" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M12" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>391</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I12" s="27" t="s">
-        <v>387</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N12" s="18" t="s">
         <v>28</v>
@@ -5642,36 +5716,36 @@
         <v>3</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M13" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G13" s="27" t="s">
-        <v>391</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I13" s="27" t="s">
-        <v>389</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N13" s="18" t="s">
         <v>28</v>
@@ -5684,36 +5758,36 @@
         <v>4</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I14" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M14" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>391</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I14" s="27" t="s">
-        <v>393</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N14" s="18" t="s">
         <v>28</v>
@@ -5723,7 +5797,7 @@
     </row>
     <row r="16" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="52" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B16" s="40"/>
       <c r="C16" s="40"/>
@@ -5746,36 +5820,36 @@
         <v>1</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I17" s="27" t="s">
+        <v>374</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M17" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>395</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I17" s="27" t="s">
-        <v>380</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L17" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N17" s="18" t="s">
         <v>28</v>
@@ -5788,40 +5862,40 @@
         <v>2</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E18" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I18" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L18" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M18" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>395</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I18" s="27" t="s">
-        <v>387</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N18" s="18" t="s">
         <v>28</v>
@@ -5831,7 +5905,7 @@
     </row>
     <row r="20" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="53" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B20" s="40"/>
       <c r="C20" s="40"/>
@@ -5851,7 +5925,7 @@
     </row>
     <row r="21" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="52" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="40"/>
@@ -5874,40 +5948,40 @@
         <v>1</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C22" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G22" s="27" t="s">
         <v>385</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="E22" s="10" t="s">
+      <c r="H22" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I22" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M22" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G22" s="27" t="s">
-        <v>391</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I22" s="27" t="s">
-        <v>387</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L22" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N22" s="18" t="s">
         <v>28</v>
@@ -5920,36 +5994,36 @@
         <v>2</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
       <c r="E23" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G23" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I23" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M23" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G23" s="27" t="s">
-        <v>391</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I23" s="27" t="s">
-        <v>389</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L23" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M23" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N23" s="18" t="s">
         <v>28</v>
@@ -5962,36 +6036,36 @@
         <v>3</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I24" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M24" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G24" s="27" t="s">
-        <v>391</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I24" s="27" t="s">
-        <v>393</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K24" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L24" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N24" s="18" t="s">
         <v>28</v>
@@ -6001,7 +6075,7 @@
     </row>
     <row r="26" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="52" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B26" s="40"/>
       <c r="C26" s="40"/>
@@ -6024,36 +6098,36 @@
         <v>1</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
       <c r="E27" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G27" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I27" s="27" t="s">
+        <v>395</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M27" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G27" s="27" t="s">
-        <v>400</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I27" s="27" t="s">
-        <v>401</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M27" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N27" s="18" t="s">
         <v>28</v>
@@ -6066,36 +6140,36 @@
         <v>2</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
       <c r="E28" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G28" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I28" s="27" t="s">
+        <v>397</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M28" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G28" s="27" t="s">
-        <v>400</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I28" s="27" t="s">
-        <v>403</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L28" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M28" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N28" s="18" t="s">
         <v>28</v>
@@ -6108,36 +6182,36 @@
         <v>3</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
       <c r="E29" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G29" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I29" s="27" t="s">
+        <v>399</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M29" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G29" s="27" t="s">
-        <v>400</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I29" s="27" t="s">
-        <v>405</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L29" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N29" s="18" t="s">
         <v>28</v>
@@ -6147,7 +6221,7 @@
     </row>
     <row r="31" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="52" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B31" s="40"/>
       <c r="C31" s="40"/>
@@ -6170,36 +6244,36 @@
         <v>1</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
       <c r="E32" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G32" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I32" s="27" t="s">
+        <v>395</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L32" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M32" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G32" s="27" t="s">
-        <v>400</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I32" s="27" t="s">
-        <v>401</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L32" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M32" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N32" s="18" t="s">
         <v>28</v>
@@ -6212,36 +6286,36 @@
         <v>2</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
       <c r="E33" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G33" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I33" s="27" t="s">
+        <v>397</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M33" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G33" s="27" t="s">
-        <v>400</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I33" s="27" t="s">
-        <v>403</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M33" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N33" s="18" t="s">
         <v>28</v>
@@ -6254,36 +6328,36 @@
         <v>3</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
       <c r="E34" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G34" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I34" s="27" t="s">
+        <v>399</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L34" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M34" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G34" s="27" t="s">
-        <v>400</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I34" s="27" t="s">
-        <v>405</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L34" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M34" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N34" s="18" t="s">
         <v>28</v>
@@ -6293,7 +6367,7 @@
     </row>
     <row r="36" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="52" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B36" s="40"/>
       <c r="C36" s="40"/>
@@ -6316,40 +6390,40 @@
         <v>1</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E37" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="G37" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I37" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="M37" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G37" s="27" t="s">
-        <v>395</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="I37" s="27" t="s">
-        <v>387</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K37" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="L37" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="N37" s="18" t="s">
         <v>28</v>
@@ -6388,21 +6462,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -6410,41 +6484,41 @@
         <v>255</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -6452,83 +6526,83 @@
         <v>23</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -6536,55 +6610,55 @@
         <v>46</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -6606,29 +6680,29 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6636,10 +6710,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D5" s="22" t="s">
         <v>84</v>
@@ -6651,13 +6725,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="E6" s="23"/>
     </row>
@@ -6666,16 +6740,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D7" s="22" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6683,10 +6757,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>454</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>460</v>
       </c>
       <c r="D8" s="22" t="s">
         <v>50</v>
@@ -6698,13 +6772,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="E9" s="23"/>
     </row>
@@ -6713,13 +6787,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="E10" s="23"/>
     </row>
@@ -6728,16 +6802,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6745,16 +6819,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6762,16 +6836,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6779,13 +6853,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="E14" s="23"/>
     </row>
@@ -6794,13 +6868,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E15" s="23"/>
     </row>
@@ -6809,13 +6883,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="E16" s="23"/>
     </row>
@@ -6824,157 +6898,157 @@
         <v>13</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D17" s="22" t="s">
         <v>254</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B20" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C20" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="D20" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="E20" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B21" t="s">
+        <v>483</v>
+      </c>
+      <c r="C21" t="s">
+        <v>488</v>
+      </c>
+      <c r="D21" t="s">
         <v>489</v>
       </c>
-      <c r="C21" t="s">
-        <v>494</v>
-      </c>
-      <c r="D21" t="s">
-        <v>495</v>
-      </c>
       <c r="E21" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B22" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C22" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="D22" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="E22" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B23" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C23" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="D23" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="E23" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B24" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C24" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="D24" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="E24" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B25" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C25" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="D25" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="E25" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B26" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C26" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D26" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="E26" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B27" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C27" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="D27" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="E27" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
